--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="C9" t="n">
         <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="C15" t="n">
         <v>3.4</v>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="C9" t="n">
         <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -596,458 +596,398 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="C11" t="n">
         <v>3.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.57</v>
-      </c>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.62</v>
-      </c>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.5</v>
-      </c>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.5</v>
-      </c>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.6</v>
-      </c>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.5</v>
-      </c>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.55</v>
-      </c>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.25</v>
-      </c>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.15</v>
-      </c>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.75</v>
-      </c>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="C22" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="D22" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D23" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.33</v>
+        <v>1.48</v>
       </c>
       <c r="C24" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="C25" t="n">
         <v>3.4</v>
       </c>
       <c r="D25" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="C26" t="n">
         <v>3.6</v>
       </c>
       <c r="D26" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>1.65</v>
       </c>
       <c r="C27" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D27" t="n">
-        <v>1.57</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="C28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="C29" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="C30" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="C31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="C32" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D33" t="n">
         <v>2.2</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="C34" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D34" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="C35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D35" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1.57</v>
       </c>
       <c r="C36" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D36" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="C38" t="n">
         <v>3.4</v>
       </c>
       <c r="D38" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="C39" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="D39" t="n">
         <v>7</v>
@@ -1056,128 +996,288 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="C40" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="D40" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="C41" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1.5</v>
       </c>
       <c r="C42" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2.25</v>
       </c>
       <c r="C43" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D43" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="C44" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="D44" t="n">
-        <v>5.75</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="C45" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="C46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D56" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C47" t="n">
+      <c r="B57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C57" t="n">
         <v>4</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D57" t="n">
         <v>4.75</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="n">
         <v>3.4</v>
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="C6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -599,26 +599,32 @@
         <v>5.25</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -628,656 +634,544 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.55</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.73</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="C22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D22" t="n">
         <v>4.75</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="C23" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.48</v>
+        <v>3.9</v>
       </c>
       <c r="C24" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="C25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D25" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="C26" t="n">
         <v>3.6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="D27" t="n">
-        <v>4.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="C28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D28" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
       <c r="C29" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="D29" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="C30" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="D30" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="C31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="C32" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="C33" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D34" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="C35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D35" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="C36" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="C37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D37" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="C38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D38" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="C39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="D40" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="C41" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D41" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="C42" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="D42" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="C43" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="D43" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="C44" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="C45" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D45" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D46" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="C47" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D48" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>2</v>
-      </c>
-      <c r="C50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D50" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C52" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D52" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C53" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C54" t="n">
-        <v>4</v>
-      </c>
-      <c r="D54" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D55" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C56" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D56" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C57" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" t="n">
         <v>4.75</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         <v>1.22</v>
       </c>
       <c r="C4" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="n">
         <v>3.4</v>
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="C8" t="n">
         <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="C9" t="n">
         <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -599,10 +599,10 @@
         <v>5.25</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12">
@@ -708,577 +708,561 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.57</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="D22" t="n">
-        <v>4.5</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>1.42</v>
       </c>
       <c r="C23" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D23" t="n">
-        <v>1.57</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="C24" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="C25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D25" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="C26" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D26" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="C27" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D27" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="C28" t="n">
         <v>3.6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="C29" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D29" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="C30" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D30" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.5</v>
+        <v>1.73</v>
       </c>
       <c r="C31" t="n">
         <v>3.6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="C32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D32" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="C33" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="C34" t="n">
         <v>3.5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="C35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D35" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D36" t="n">
         <v>1.57</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D36" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D37" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="C38" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D38" t="n">
-        <v>2.38</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="C39" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="C40" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D40" t="n">
-        <v>6.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="C41" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="C42" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="D42" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="C43" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D43" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D44" t="n">
         <v>2.45</v>
-      </c>
-      <c r="C44" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="C45" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D46" t="n">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="C47" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="C48" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D48" t="n">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="D49" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D50" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="C51" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D51" t="n">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="C52" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="D52" t="n">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="C53" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="D53" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D54" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="C55" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="D55" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="C56" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D56" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C57" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,87 +448,87 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.57</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="C6" t="n">
-        <v>5.25</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -538,87 +538,93 @@
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="D8" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>3.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -628,7 +634,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -638,7 +644,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -648,7 +654,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -658,7 +664,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -668,7 +674,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -678,7 +684,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -688,7 +694,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -698,7 +704,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -708,561 +714,405 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.55</v>
-      </c>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.42</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D23" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>dUjtW2Fr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="C24" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D24" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>MFnpCm7C</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.35</v>
+        <v>5.5</v>
       </c>
       <c r="C25" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>Wn71woN8</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.65</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="D26" t="n">
-        <v>4.5</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>UsklUtpe</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="C27" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D27" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="C28" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D28" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>OrHrRGXo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
       <c r="C30" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D30" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>EkqxE9x0</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="C31" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>dAfPwfHi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="C32" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="D32" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>pWQ6LC1N</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="C33" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>jiUEFsV1</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
         <v>1.57</v>
-      </c>
-      <c r="C35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D35" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="C36" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.57</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.3</v>
-      </c>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>vDA9yPiL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="C38" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>hzeTFV7m</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="C39" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D39" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>Q9rcSKE7</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="C40" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D40" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="C41" t="n">
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="C42" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D42" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>QkntzCGG</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="C43" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="D43" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="C44" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="D44" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>ddFjPf2b</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>4.75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>hxlYyYo4</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="C46" t="n">
         <v>3.6</v>
       </c>
       <c r="D46" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>GEugARyP</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="C47" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="D47" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>2</v>
-      </c>
-      <c r="C49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D49" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D51" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D53" t="n">
         <v>4.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D54" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,821 +448,721 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5.75</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>2.15</v>
       </c>
       <c r="C3" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>1.09</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>2.88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="C6" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D8" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="C10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.25</v>
+        <v>1.25</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.42</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.86</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.82</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>rRQ6H30k</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="C22" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.55</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>dUjtW2Fr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.42</v>
+        <v>3.5</v>
       </c>
       <c r="C23" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D23" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MFnpCm7C</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="C24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>UsklUtpe</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="C25" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D25" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>ddFjPf2b</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="C26" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.35</v>
+        <v>1.61</v>
       </c>
       <c r="C27" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D27" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>dAfPwfHi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.88</v>
+        <v>1.33</v>
       </c>
       <c r="C28" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>pWQ6LC1N</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="C29" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D29" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>jiUEFsV1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.73</v>
+        <v>5.5</v>
       </c>
       <c r="C31" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>4.75</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="C32" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="D32" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>vDA9yPiL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="C33" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>hzeTFV7m</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D34" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>Q9rcSKE7</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.57</v>
+        <v>3.75</v>
       </c>
       <c r="C35" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="C36" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D36" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>QkntzCGG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="C37" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D37" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>Wn71woN8</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="D38" t="n">
-        <v>7.5</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EkqxE9x0</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="C39" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>GEugARyP</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="C40" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D40" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="C42" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D42" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>OrHrRGXo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.45</v>
+        <v>9</v>
       </c>
       <c r="C43" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="C44" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="D45" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>hxlYyYo4</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="C46" t="n">
         <v>3.6</v>
       </c>
       <c r="D46" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D47" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>2</v>
-      </c>
-      <c r="C49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D49" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D51" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D53" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D54" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C3" t="n">
         <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -599,7 +599,7 @@
         <v>1.25</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="C12" t="n">
-        <v>5.59</v>
+        <v>6.2</v>
       </c>
       <c r="D12" t="n">
-        <v>9.15</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="C13" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="D13" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="C14" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="D14" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="C15" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="16">
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="C16" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="D16" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="C17" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="D17" t="n">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="18">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="C18" t="n">
-        <v>5.74</v>
+        <v>5.8</v>
       </c>
       <c r="D18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="C19" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="20">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="C20" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -756,413 +756,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="D21" t="n">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>rRQ6H30k</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>dUjtW2Fr</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>MFnpCm7C</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>UsklUtpe</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddFjPf2b</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Sh9BS8ig</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>dAfPwfHi</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>pWQ6LC1N</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>jiUEFsV1</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>dY0SOQjI</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C31" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>hO8aNYWA</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D32" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>vDA9yPiL</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>hzeTFV7m</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Q9rcSKE7</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>zJCJQnM5</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>QkntzCGG</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D37" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Wn71woN8</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkqxE9x0</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>GEugARyP</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D40" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>U32wGjPp</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>hGzqjO6E</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>OrHrRGXo</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>9</v>
-      </c>
-      <c r="C43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>WQF2UUMt</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>rkazN4LU</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D45" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>hxlYyYo4</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="C3" t="n">
         <v>3.6</v>
@@ -487,10 +487,10 @@
         <v>1.8</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -548,221 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
         <v>1.73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ERWFdKZh</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="C12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8QPOfb45</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>x6HuiG3U</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,113 +448,209 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="C4" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>4.33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D7" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C12" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>1.73</v>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,209 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.22</v>
+        <v>2.7</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D9" t="n">
         <v>4.75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="C11" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="C3" t="n">
         <v>3.9</v>
       </c>
       <c r="D3" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="C4" t="n">
         <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         <v>4.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="C9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D9" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="C2" t="n">
         <v>5.25</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         <v>3.9</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>2.9</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
         <v>2.35</v>
@@ -519,7 +519,7 @@
         <v>4.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D6" t="n">
         <v>1.73</v>
@@ -535,10 +535,10 @@
         <v>2.05</v>
       </c>
       <c r="C7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D7" t="n">
         <v>3.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="9">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="C9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -596,13 +596,141 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D11" t="n">
         <v>1.85</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,289 +448,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="C2" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2kGeEq1e</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2TvL16Hk</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>tzSnG5Wr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Wplk7SgS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AVat9lPF</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,49 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2.55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="C4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C8" t="n">
         <v>4.2</v>
       </c>
-      <c r="D4" t="n">
-        <v>1.83</v>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         <v>4.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="C3" t="n">
         <v>4.75</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="C10" t="n">
         <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -603,6 +603,166 @@
       </c>
       <c r="D11" t="n">
         <v>2.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,321 +448,33 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2kGeEq1e</t>
+          <t>AFJ3CNV7</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2TvL16Hk</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tzSnG5Wr</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Wplk7SgS</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>AVat9lPF</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AFJ3CNV7</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
           <t>Of1jzRNE</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>C0axT3Xo</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>d8abY4hR</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>pYXoP0FD</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B3" t="n">
         <v>3.6</v>
       </c>
-      <c r="D14" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>xtzXn47K</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="C3" t="n">
         <v>3.6</v>
       </c>
-      <c r="D15" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dQG3srVs</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Q58Kw0U6</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>W2BSyvaJ</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OIqwRMp1</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>GhtVSrGl</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>UwFBuMaf</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.8</v>
+      <c r="D3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,33 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3.2</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C10" t="n">
         <v>3.6</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D10" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C11" t="n">
         <v>3.6</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
+      <c r="D11" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D3" t="n">
         <v>5.25</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C4" t="n">
         <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="C7" t="n">
         <v>3.5</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="C8" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
         <v>4.75</v>
@@ -596,173 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="C11" t="n">
         <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
         <v>4.75</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>7</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,33 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>8MkyzwoT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>GhdgPLWA</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C15" t="n">
         <v>3.6</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D15" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C18" t="n">
         <v>3.6</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D18" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         <v>5.25</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
         <v>1.6</v>
@@ -471,7 +471,7 @@
         <v>1.17</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="C4" t="n">
         <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="C5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D6" t="n">
         <v>2.63</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.55</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D8" t="n">
         <v>1.36</v>
@@ -567,10 +567,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -586,183 +586,7 @@
         <v>3.75</v>
       </c>
       <c r="D10" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>SQM1jbV9</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bFdtqGNq</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>l0Zi1FqS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8MkyzwoT</t>
+          <t>KnvLwLo4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GhdgPLWA</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>l6f1Na1N</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,49 +448,257 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>r3Wq3yFF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>SQM1jbV9</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.3</v>
+        <v>1.14</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>bFdtqGNq</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>1.6</v>
       </c>
-      <c r="C4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.25</v>
+      <c r="C15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,257 +448,193 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r3Wq3yFF</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.25</v>
+        <v>2.15</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.25</v>
+        <v>2.45</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D7" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="D8" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="C10" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="D12" t="n">
-        <v>5.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="C13" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D15" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,193 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="C5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D5" t="n">
         <v>4.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6</v>
+        <v>4.75</v>
       </c>
       <c r="C8" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="D9" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="C11" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="C12" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.29</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="C13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -458,7 +458,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="C3" t="n">
         <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="C4" t="n">
         <v>3.3</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="C5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="D5" t="n">
         <v>4.5</v>
@@ -522,7 +522,7 @@
         <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>3.9</v>
@@ -567,10 +567,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="10">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="C10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>4.75</v>
@@ -602,7 +602,7 @@
         <v>3.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="C12" t="n">
         <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="13">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="C14" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="15">
@@ -695,7 +695,7 @@
         <v>2.7</v>
       </c>
       <c r="C17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D17" t="n">
         <v>2.6</v>
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="C19" t="n">
         <v>3.6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -762,7 +762,7 @@
         <v>3.4</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>1.95</v>
       </c>
       <c r="C6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D6" t="n">
         <v>3.6</v>
@@ -554,7 +554,7 @@
         <v>3.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="C12" t="n">
         <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="C14" t="n">
         <v>4.2</v>
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="20">

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,39 +448,39 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.48</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="C3" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -491,278 +491,6 @@
       </c>
       <c r="D4" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ShJjaSDs</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>SSZaQ4Ct</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2ot8gOsJ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KMCY9qSa</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>v5b6XwQN</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ABRGMMB5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>rPPOK0tI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>viJXIvBU</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zypxSHmo</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="C16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>rw5cZaeB</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EcDtwrdn</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zD1kyMQb</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>EJlHkLuh</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>EqY7Orsg</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,49 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="D3" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="C4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C7" t="n">
         <v>3.3</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
+      <c r="D7" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="C4" t="n">
         <v>4.33</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="C5" t="n">
         <v>4.5</v>
       </c>
       <c r="D5" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="C6" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C9" t="n">
         <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.8</v>
       </c>
       <c r="D9" t="n">
         <v>1.8</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="C10" t="n">
         <v>3.75</v>
@@ -596,173 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="D11" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>WIs9mjGL</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>MqhPmaA4</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lb85TUOk</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rc1ER8g2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>21YvrUwq</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OGMmt88e</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EJ4unbdE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>drzevnw8</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>zil0kCo9</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ratYowuH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,161 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>WIs9mjGL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>MqhPmaA4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.85</v>
+        <v>5.75</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>lb85TUOk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="C4" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>rc1ER8g2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="C5" t="n">
         <v>4.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>21YvrUwq</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.11</v>
+        <v>2.15</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>OGMmt88e</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="C7" t="n">
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>EJ4unbdE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C9" t="n">
         <v>4.1</v>
       </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="C10" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>nX2mpxRQ</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YTzyyYmD</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>K0RAmBXI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0d4cBEPP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HqKvGll</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0zTMbytK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KK9ggF3s</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hY71igYg</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
         <v>2.5</v>
       </c>
-      <c r="C11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D11" t="n">
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>CzO2kX26</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CEnSxfJ0</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>2.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="C7" t="n">
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="C8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="C9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
@@ -583,7 +583,7 @@
         <v>2.6</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D10" t="n">
         <v>2.6</v>
@@ -599,170 +599,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D11" t="n">
         <v>3.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>nX2mpxRQ</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>YTzyyYmD</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>K0RAmBXI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0d4cBEPP</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HqKvGll</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0zTMbytK</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KK9ggF3s</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hY71igYg</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>CzO2kX26</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CEnSxfJ0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,161 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="D10" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="C11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/england/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
         <v>2.7</v>
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="C5" t="n">
         <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="C8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="D8" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="n">
         <v>2.63</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.55</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="C10" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,125 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="C11" t="n">
         <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EubK3NNG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Cl3y4WHa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p21q2AnC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WveT5hmm</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v3JHq2Wp</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>69B375Oi</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>A7iT11hT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
